--- a/all_labels_extract.xlsx
+++ b/all_labels_extract.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snakada/Documents/univ/Peru_work/code_endes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05113F2C-6AF6-CC4D-9F17-188C3376416D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCC32C4-31C6-6244-85ED-0817502537CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1172,9 +1172,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1664,6 +1665,9 @@
       <c r="C13" t="s">
         <v>337</v>
       </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
@@ -1675,6 +1679,9 @@
       <c r="C14" t="s">
         <v>337</v>
       </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
@@ -1686,6 +1693,9 @@
       <c r="C15" t="s">
         <v>337</v>
       </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
@@ -2004,7 +2014,7 @@
         <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D43" t="s">
         <v>350</v>
@@ -2018,7 +2028,7 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D44" t="s">
         <v>350</v>
@@ -2032,12 +2042,12 @@
         <v>64</v>
       </c>
       <c r="C45" t="s">
-        <v>335</v>
-      </c>
-      <c r="D45" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>1</v>
       </c>
     </row>
@@ -2271,7 +2281,7 @@
         <v>99</v>
       </c>
       <c r="C64" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -2285,7 +2295,7 @@
         <v>101</v>
       </c>
       <c r="C65" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2595,7 +2605,7 @@
         <v>130</v>
       </c>
       <c r="C85" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3698,12 +3708,12 @@
     </row>
     <row r="176" spans="1:6">
       <c r="C176" t="s">
-        <v>335</v>
-      </c>
-      <c r="D176" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="E176">
+      <c r="F176">
         <v>1</v>
       </c>
     </row>

--- a/all_labels_extract.xlsx
+++ b/all_labels_extract.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snakada/Documents/univ_github/peru_endes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB93C51-AD64-6844-9BAA-949CD7AD7A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C722C0-7EC2-024A-89D7-E09D3B8D0120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="500" windowWidth="19200" windowHeight="19500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10200" yWindow="760" windowWidth="19200" windowHeight="16840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="var_clean251225" sheetId="2" r:id="rId1"/>
@@ -6421,6 +6421,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A763F12F-6215-3D4A-8A4D-6CA315599238}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -7039,6 +7042,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="80" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
